--- a/lai/valuationquan/AILOF/csiAILOFmodel2meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel2meancn.xlsx
@@ -63,7 +63,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -149,10 +153,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>均线</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -173,11 +173,19 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>RSV</t>
+    <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>K</t>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSV</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -189,15 +197,15 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>K</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>成交量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -887,7 +895,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1202,6 +1210,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1211,7 +1222,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1525,6 +1536,9 @@
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>4893.7540233362733</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
               </c:numCache>
@@ -1568,7 +1582,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1883,6 +1897,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1892,7 +1909,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2206,6 +2223,9 @@
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>7246.1850032321172</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
               </c:numCache>
@@ -2249,7 +2269,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2564,6 +2584,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2573,7 +2596,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2887,6 +2910,9 @@
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>2352.4309798958438</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
               </c:numCache>
@@ -2909,11 +2935,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="625559424"/>
-        <c:axId val="691897472"/>
+        <c:axId val="558534016"/>
+        <c:axId val="558535808"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="625559424"/>
+        <c:axId val="558534016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2956,14 +2982,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691897472"/>
+        <c:crossAx val="558535808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="691897472"/>
+        <c:axId val="558535808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,7 +3038,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625559424"/>
+        <c:crossAx val="558534016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3226,7 +3252,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3541,6 +3567,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3550,7 +3579,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3864,6 +3893,9 @@
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>6052.5924500756464</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
               </c:numCache>
@@ -3907,7 +3939,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4222,6 +4254,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4231,7 +4266,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4546,6 +4581,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>11552.867619918841</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>11585.38397723743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4588,7 +4626,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4903,6 +4941,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4912,7 +4953,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5227,6 +5268,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>5500.2751698431948</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5532.791527161784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5248,11 +5292,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="563221632"/>
-        <c:axId val="563223168"/>
+        <c:axId val="578777472"/>
+        <c:axId val="578779008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="563221632"/>
+        <c:axId val="578777472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5295,14 +5339,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563223168"/>
+        <c:crossAx val="578779008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="563223168"/>
+        <c:axId val="578779008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5351,7 +5395,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563221632"/>
+        <c:crossAx val="578777472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5565,7 +5609,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5880,6 +5924,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5889,7 +5936,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6203,6 +6250,9 @@
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>4478.5830960357953</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
               </c:numCache>
@@ -6246,7 +6296,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6561,6 +6611,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6570,7 +6623,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6884,6 +6937,9 @@
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>6735.3146089982411</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
               </c:numCache>
@@ -6927,7 +6983,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7242,6 +7298,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7251,7 +7310,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7565,6 +7624,9 @@
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>2256.7315129624458</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
               </c:numCache>
@@ -7587,11 +7649,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595986688"/>
-        <c:axId val="595992576"/>
+        <c:axId val="578795008"/>
+        <c:axId val="578796544"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595986688"/>
+        <c:axId val="578795008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7634,14 +7696,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595992576"/>
+        <c:crossAx val="578796544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595992576"/>
+        <c:axId val="578796544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7690,7 +7752,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595986688"/>
+        <c:crossAx val="578795008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7904,7 +7966,7 @@
               <c:f>'模型二 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8219,6 +8281,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8228,7 +8293,7 @@
               <c:f>'模型二 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8542,6 +8607,9 @@
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>2280.0747683969207</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
               </c:numCache>
@@ -8585,7 +8653,7 @@
               <c:f>'模型二 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8900,6 +8968,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8909,7 +8980,7 @@
               <c:f>'模型二 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9223,6 +9294,9 @@
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>3181.8326442193757</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
               </c:numCache>
@@ -9266,7 +9340,7 @@
               <c:f>'模型二 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9581,6 +9655,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9590,7 +9667,7 @@
               <c:f>'模型二 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9904,6 +9981,9 @@
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>901.75787582245493</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
               </c:numCache>
@@ -9926,11 +10006,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="621133184"/>
-        <c:axId val="621151360"/>
+        <c:axId val="578857600"/>
+        <c:axId val="578871680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="621133184"/>
+        <c:axId val="578857600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9973,14 +10053,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621151360"/>
+        <c:crossAx val="578871680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621151360"/>
+        <c:axId val="578871680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10029,7 +10109,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621133184"/>
+        <c:crossAx val="578857600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10243,7 +10323,7 @@
               <c:f>'模型二 (2)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10558,6 +10638,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10567,7 +10650,7 @@
               <c:f>'模型二 (2)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10881,6 +10964,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -10924,7 +11010,7 @@
               <c:f>'模型二 (2)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11239,6 +11325,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11248,7 +11337,7 @@
               <c:f>'模型二 (2)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11562,6 +11651,9 @@
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1243.9035388429725</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
               </c:numCache>
@@ -11605,7 +11697,7 @@
               <c:f>'模型二 (2)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11920,6 +12012,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11929,7 +12024,7 @@
               <c:f>'模型二 (2)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12243,6 +12338,9 @@
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>461.2250703448251</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
               </c:numCache>
@@ -12265,11 +12363,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="621597440"/>
-        <c:axId val="621598976"/>
+        <c:axId val="580915200"/>
+        <c:axId val="580916736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="621597440"/>
+        <c:axId val="580915200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12312,14 +12410,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621598976"/>
+        <c:crossAx val="580916736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621598976"/>
+        <c:axId val="580916736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12368,7 +12466,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621597440"/>
+        <c:crossAx val="580915200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12582,7 +12680,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12897,6 +12995,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12906,7 +13007,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13220,6 +13321,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -13263,7 +13367,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13578,6 +13682,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13587,7 +13694,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13901,6 +14008,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -13944,7 +14054,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14259,6 +14369,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14268,7 +14381,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14582,6 +14695,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -14604,11 +14720,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="622004096"/>
-        <c:axId val="622005632"/>
+        <c:axId val="581514368"/>
+        <c:axId val="581515904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="622004096"/>
+        <c:axId val="581514368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14651,14 +14767,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622005632"/>
+        <c:crossAx val="581515904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="622005632"/>
+        <c:axId val="581515904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14707,7 +14823,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622004096"/>
+        <c:crossAx val="581514368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14921,7 +15037,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15236,6 +15352,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15245,7 +15364,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15559,6 +15678,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -15602,7 +15724,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15917,6 +16039,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15926,7 +16051,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16240,6 +16365,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -16283,7 +16411,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16598,6 +16726,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16607,7 +16738,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16921,6 +17052,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -16943,11 +17077,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="622705664"/>
-        <c:axId val="622707456"/>
+        <c:axId val="581728512"/>
+        <c:axId val="581865472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="622705664"/>
+        <c:axId val="581728512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16990,14 +17124,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622707456"/>
+        <c:crossAx val="581865472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="622707456"/>
+        <c:axId val="581865472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17046,7 +17180,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622705664"/>
+        <c:crossAx val="581728512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17260,7 +17394,7 @@
               <c:f>'模型二 (2)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17575,6 +17709,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17584,7 +17721,7 @@
               <c:f>'模型二 (2)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17898,6 +18035,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -17941,7 +18081,7 @@
               <c:f>'模型二 (2)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18256,6 +18396,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18265,7 +18408,7 @@
               <c:f>'模型二 (2)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18579,6 +18722,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -18622,7 +18768,7 @@
               <c:f>'模型二 (2)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18937,6 +19083,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18946,7 +19095,7 @@
               <c:f>'模型二 (2)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19260,6 +19409,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -19282,11 +19434,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="624959872"/>
-        <c:axId val="624961408"/>
+        <c:axId val="582118784"/>
+        <c:axId val="582317184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="624959872"/>
+        <c:axId val="582118784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19329,14 +19481,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624961408"/>
+        <c:crossAx val="582317184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="624961408"/>
+        <c:axId val="582317184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19385,7 +19537,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624959872"/>
+        <c:crossAx val="582118784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19493,7 +19645,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19536,7 +19688,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19579,7 +19731,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19622,7 +19774,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19665,7 +19817,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19708,7 +19860,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19751,7 +19903,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19794,7 +19946,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20107,7 +20259,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20142,37 +20294,37 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="12"/>
     </row>
@@ -20198,7 +20350,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -20249,28 +20401,28 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X4" s="6">
         <v>43098</v>
@@ -24588,6 +24740,41 @@
         <v>2352.4309798958438</v>
       </c>
       <c r="K108" s="21">
+        <v>7246.1850032321172</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>4893.7540233362733</v>
+      </c>
+      <c r="I109" s="22">
+        <v>7246.1850032321172</v>
+      </c>
+      <c r="J109" s="22">
+        <v>2352.4309798958438</v>
+      </c>
+      <c r="K109" s="21">
         <v>7246.1850032321172</v>
       </c>
     </row>
@@ -24607,7 +24794,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24642,37 +24829,37 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>23</v>
@@ -24709,7 +24896,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -24770,28 +24957,28 @@
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -30356,6 +30543,53 @@
         <v>67.765986815617211</v>
       </c>
       <c r="O108" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>-405.63347659313405</v>
+      </c>
+      <c r="E109" s="22">
+        <v>-155.89295806705468</v>
+      </c>
+      <c r="F109" s="22">
+        <v>5.0791853840317174</v>
+      </c>
+      <c r="G109" s="22">
+        <v>13.216040359562751</v>
+      </c>
+      <c r="H109" s="22">
+        <v>6052.5924500756464</v>
+      </c>
+      <c r="I109" s="22">
+        <v>11585.38397723743</v>
+      </c>
+      <c r="J109" s="22">
+        <v>5532.791527161784</v>
+      </c>
+      <c r="K109" s="21">
+        <v>11572.167936877868</v>
+      </c>
+      <c r="L109" s="26">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.035028220618088</v>
+      </c>
+      <c r="O109" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -30377,7 +30611,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30412,49 +30646,49 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P1" s="14" t="s">
         <v>26</v>
@@ -30482,7 +30716,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -30547,28 +30781,28 @@
         <v>0.95</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -36402,6 +36636,56 @@
         <v>67.813131608977557</v>
       </c>
       <c r="P108" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>4478.5830960357953</v>
+      </c>
+      <c r="I109" s="22">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="J109" s="22">
+        <v>2256.7315129624458</v>
+      </c>
+      <c r="K109" s="21">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="L109" s="26">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="M109" s="27">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="O109" s="27">
+        <v>78.982013449904031</v>
+      </c>
+      <c r="P109" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -36423,7 +36707,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36463,43 +36747,43 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O1" s="12"/>
     </row>
@@ -36529,7 +36813,7 @@
         <v>1550</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
@@ -36586,28 +36870,28 @@
       </c>
       <c r="N4" s="7"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -41549,6 +41833,47 @@
         <v>901.75787582245493</v>
       </c>
       <c r="M108" s="21">
+        <v>3181.8326442193757</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="20">
+        <v>1392651</v>
+      </c>
+      <c r="E109" s="20">
+        <v>1884139.3069248656</v>
+      </c>
+      <c r="F109" s="21">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22">
+        <v>2280.0747683969207</v>
+      </c>
+      <c r="K109" s="22">
+        <v>3181.8326442193757</v>
+      </c>
+      <c r="L109" s="22">
+        <v>901.75787582245493</v>
+      </c>
+      <c r="M109" s="21">
         <v>3181.8326442193757</v>
       </c>
     </row>
@@ -41570,7 +41895,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41605,37 +41930,37 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="12"/>
     </row>
@@ -41661,7 +41986,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -41712,28 +42037,28 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X4" s="6">
         <v>43098</v>
@@ -46051,6 +46376,41 @@
         <v>461.2250703448251</v>
       </c>
       <c r="K108" s="21">
+        <v>1243.9035388429725</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1243.9035388429725</v>
+      </c>
+      <c r="J109" s="22">
+        <v>461.2250703448251</v>
+      </c>
+      <c r="K109" s="21">
         <v>1243.9035388429725</v>
       </c>
     </row>
@@ -46072,7 +46432,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46107,37 +46467,37 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>23</v>
@@ -46174,7 +46534,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -46235,28 +46595,28 @@
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -51821,6 +52181,53 @@
         <v>67.765986815617211</v>
       </c>
       <c r="O108" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="21">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J109" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L109" s="26">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="M109" s="27">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.035028220618088</v>
+      </c>
+      <c r="O109" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -51842,7 +52249,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -51877,49 +52284,49 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P1" s="14" t="s">
         <v>26</v>
@@ -51947,7 +52354,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -52012,28 +52419,28 @@
         <v>0.95</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -57866,6 +58273,56 @@
         <v>67.813131608977557</v>
       </c>
       <c r="P108" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I109" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J109" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K109" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L109" s="26">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="M109" s="27">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="N109" s="27">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="O109" s="27">
+        <v>78.982013449904031</v>
+      </c>
+      <c r="P109" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -57887,7 +58344,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -57927,43 +58384,43 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O1" s="12"/>
     </row>
@@ -57993,7 +58450,7 @@
         <v>1550</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
@@ -58050,28 +58507,28 @@
       </c>
       <c r="N4" s="7"/>
       <c r="Q4" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" s="32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X4" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -63013,6 +63470,47 @@
         <v>212.99681655802686</v>
       </c>
       <c r="M108" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="12.75">
+      <c r="A109" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B109" s="25">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.293504912308348</v>
+      </c>
+      <c r="D109" s="20">
+        <v>1392651</v>
+      </c>
+      <c r="E109" s="20">
+        <v>1884139.3069248656</v>
+      </c>
+      <c r="F109" s="21">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K109" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L109" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M109" s="21">
         <v>579.4237932103814</v>
       </c>
     </row>

--- a/lai/valuationquan/AILOF/csiAILOFmodel2meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel2meancn.xlsx
@@ -63,11 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
-  <si>
-    <t>K</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -153,8 +149,16 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>均线</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SMA之MAX</t>
@@ -173,19 +177,11 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>RSV</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业LOF</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RSV</t>
+    <t>K</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -197,7 +193,15 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>K</t>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>均线</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -895,7 +899,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1213,6 +1217,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1222,7 +1229,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1539,6 +1546,9 @@
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>4893.7540233362733</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>4893.7540233362733</c:v>
                 </c:pt>
               </c:numCache>
@@ -1582,7 +1592,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1900,6 +1910,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1909,7 +1922,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2226,6 +2239,9 @@
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>7246.1850032321172</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>7246.1850032321172</c:v>
                 </c:pt>
               </c:numCache>
@@ -2269,7 +2285,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2587,6 +2603,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2596,7 +2615,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2913,6 +2932,9 @@
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>2352.4309798958438</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>2352.4309798958438</c:v>
                 </c:pt>
               </c:numCache>
@@ -2935,11 +2957,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558534016"/>
-        <c:axId val="558535808"/>
+        <c:axId val="528297984"/>
+        <c:axId val="528299520"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558534016"/>
+        <c:axId val="528297984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2982,14 +3004,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558535808"/>
+        <c:crossAx val="528299520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558535808"/>
+        <c:axId val="528299520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3038,7 +3060,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558534016"/>
+        <c:crossAx val="528297984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3252,7 +3274,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3570,6 +3592,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3579,7 +3604,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3896,6 +3921,9 @@
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>6052.5924500756464</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>6052.5924500756464</c:v>
                 </c:pt>
               </c:numCache>
@@ -3939,7 +3967,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4257,6 +4285,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4266,7 +4297,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4584,6 +4615,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>11585.38397723743</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>11584.987800428717</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4626,7 +4660,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4944,6 +4978,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4953,7 +4990,7 @@
               <c:f>'模型二 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5271,6 +5308,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>5532.791527161784</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5532.3953503530702</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5292,11 +5332,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578777472"/>
-        <c:axId val="578779008"/>
+        <c:axId val="489709568"/>
+        <c:axId val="489711104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578777472"/>
+        <c:axId val="489709568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5339,14 +5379,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578779008"/>
+        <c:crossAx val="489711104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578779008"/>
+        <c:axId val="489711104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5395,7 +5435,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578777472"/>
+        <c:crossAx val="489709568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5609,7 +5649,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5927,6 +5967,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5936,7 +5979,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6253,6 +6296,9 @@
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>4478.5830960357953</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>4478.5830960357953</c:v>
                 </c:pt>
               </c:numCache>
@@ -6296,7 +6342,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6614,6 +6660,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6623,7 +6672,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6940,6 +6989,9 @@
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>6735.3146089982411</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>6735.3146089982411</c:v>
                 </c:pt>
               </c:numCache>
@@ -6983,7 +7035,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7301,6 +7353,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7310,7 +7365,7 @@
               <c:f>'模型二 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7627,6 +7682,9 @@
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>2256.7315129624458</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>2256.7315129624458</c:v>
                 </c:pt>
               </c:numCache>
@@ -7649,11 +7707,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578795008"/>
-        <c:axId val="578796544"/>
+        <c:axId val="489727104"/>
+        <c:axId val="489728640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578795008"/>
+        <c:axId val="489727104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7696,14 +7754,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578796544"/>
+        <c:crossAx val="489728640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578796544"/>
+        <c:axId val="489728640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7752,7 +7810,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578795008"/>
+        <c:crossAx val="489727104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7966,7 +8024,7 @@
               <c:f>'模型二 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8284,6 +8342,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8293,7 +8354,7 @@
               <c:f>'模型二 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8610,6 +8671,9 @@
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>2280.0747683969207</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>2280.0747683969207</c:v>
                 </c:pt>
               </c:numCache>
@@ -8653,7 +8717,7 @@
               <c:f>'模型二 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8971,6 +9035,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8980,7 +9047,7 @@
               <c:f>'模型二 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9297,6 +9364,9 @@
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>3181.8326442193757</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>3181.8326442193757</c:v>
                 </c:pt>
               </c:numCache>
@@ -9340,7 +9410,7 @@
               <c:f>'模型二 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9658,6 +9728,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9667,7 +9740,7 @@
               <c:f>'模型二 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9984,6 +10057,9 @@
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>901.75787582245493</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>901.75787582245493</c:v>
                 </c:pt>
               </c:numCache>
@@ -10006,11 +10082,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578857600"/>
-        <c:axId val="578871680"/>
+        <c:axId val="495184128"/>
+        <c:axId val="495259648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578857600"/>
+        <c:axId val="495184128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10053,14 +10129,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578871680"/>
+        <c:crossAx val="495259648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578871680"/>
+        <c:axId val="495259648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10109,7 +10185,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578857600"/>
+        <c:crossAx val="495184128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10323,7 +10399,7 @@
               <c:f>'模型二 (2)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10641,6 +10717,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10650,7 +10729,7 @@
               <c:f>'模型二 (2)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10967,6 +11046,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -11010,7 +11092,7 @@
               <c:f>'模型二 (2)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11328,6 +11410,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11337,7 +11422,7 @@
               <c:f>'模型二 (2)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11654,6 +11739,9 @@
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1243.9035388429725</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1243.9035388429725</c:v>
                 </c:pt>
               </c:numCache>
@@ -11697,7 +11785,7 @@
               <c:f>'模型二 (2)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12015,6 +12103,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12024,7 +12115,7 @@
               <c:f>'模型二 (2)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12341,6 +12432,9 @@
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>461.2250703448251</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>461.2250703448251</c:v>
                 </c:pt>
               </c:numCache>
@@ -12363,11 +12457,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="580915200"/>
-        <c:axId val="580916736"/>
+        <c:axId val="495304064"/>
+        <c:axId val="495309952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="580915200"/>
+        <c:axId val="495304064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12410,14 +12504,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="580916736"/>
+        <c:crossAx val="495309952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="580916736"/>
+        <c:axId val="495309952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12466,7 +12560,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="580915200"/>
+        <c:crossAx val="495304064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12680,7 +12774,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12998,6 +13092,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13007,7 +13104,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13324,6 +13421,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -13367,7 +13467,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13685,6 +13785,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13694,7 +13797,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14011,6 +14114,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -14054,7 +14160,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14372,6 +14478,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14381,7 +14490,7 @@
               <c:f>'模型二 (2)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14698,6 +14807,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -14720,11 +14832,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581514368"/>
-        <c:axId val="581515904"/>
+        <c:axId val="496837376"/>
+        <c:axId val="496838912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581514368"/>
+        <c:axId val="496837376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14767,14 +14879,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581515904"/>
+        <c:crossAx val="496838912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581515904"/>
+        <c:axId val="496838912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14823,7 +14935,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581514368"/>
+        <c:crossAx val="496837376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15037,7 +15149,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15355,6 +15467,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15364,7 +15479,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15681,6 +15796,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -15724,7 +15842,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16042,6 +16160,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16051,7 +16172,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16368,6 +16489,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -16411,7 +16535,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16729,6 +16853,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16738,7 +16865,7 @@
               <c:f>'模型二 (2)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17055,6 +17182,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -17077,11 +17207,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581728512"/>
-        <c:axId val="581865472"/>
+        <c:axId val="497878912"/>
+        <c:axId val="497880448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581728512"/>
+        <c:axId val="497878912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17124,14 +17254,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581865472"/>
+        <c:crossAx val="497880448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581865472"/>
+        <c:axId val="497880448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17180,7 +17310,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581728512"/>
+        <c:crossAx val="497878912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17399,7 +17529,7 @@
                   <c:v>42853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42886</c:v>
+                  <c:v>46080</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>42916</c:v>
@@ -17726,319 +17856,319 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57621376243097611</c:v>
+                  <c:v>0.53243165671554316</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.7189492664455148</c:v>
+                  <c:v>7.6751671607300818</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.844583366399293</c:v>
+                  <c:v>13.80080126068386</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.844583366399293</c:v>
+                  <c:v>13.80080126068386</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13.844583366399293</c:v>
+                  <c:v>13.80080126068386</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15.988117091151651</c:v>
+                  <c:v>15.944334985436218</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>41.04379200578655</c:v>
+                  <c:v>41.00000990007112</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46.70014581694987</c:v>
+                  <c:v>46.656363711234441</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>57.492905231276332</c:v>
+                  <c:v>57.449123125560902</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>92.2491255464613</c:v>
+                  <c:v>92.205343440745878</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>172.30060647719367</c:v>
+                  <c:v>172.25682437147825</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>228.9714047240133</c:v>
+                  <c:v>228.92762261829787</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>263.30019012675183</c:v>
+                  <c:v>263.25640802103641</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>300.33791455050084</c:v>
+                  <c:v>300.29413244478542</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>303.32313139384269</c:v>
+                  <c:v>303.27934928812726</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>303.32313139384269</c:v>
+                  <c:v>303.27934928812726</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>303.32313139384269</c:v>
+                  <c:v>303.27934928812726</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>305.35027235124119</c:v>
+                  <c:v>305.30649024552577</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>306.43608747875834</c:v>
+                  <c:v>306.39230537304292</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>307.33762163901605</c:v>
+                  <c:v>307.29383953330063</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>307.50765051667753</c:v>
+                  <c:v>307.46386841096211</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>307.50765051667753</c:v>
+                  <c:v>307.46386841096211</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>307.50765051667753</c:v>
+                  <c:v>307.46386841096211</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>308.28621714077974</c:v>
+                  <c:v>308.24243503506432</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>313.60003528991899</c:v>
+                  <c:v>313.55625318420357</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>316.4535834723722</c:v>
+                  <c:v>316.40980136665678</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>316.71089770248</c:v>
+                  <c:v>316.66711559676457</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>317.51541321901169</c:v>
+                  <c:v>317.47163111329627</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>317.73541628871601</c:v>
+                  <c:v>317.69163418300059</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>317.74076568201389</c:v>
+                  <c:v>317.69698357629846</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>317.75778856327963</c:v>
+                  <c:v>317.71400645756421</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>346.12732616203544</c:v>
+                  <c:v>346.08354405632002</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>346.35166585996393</c:v>
+                  <c:v>346.30788375424851</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>346.43120812626563</c:v>
+                  <c:v>346.38742602055021</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>346.43120812626563</c:v>
+                  <c:v>346.38742602055021</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>347.15757819781584</c:v>
+                  <c:v>347.11379609210042</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>347.83889366468429</c:v>
+                  <c:v>347.79511155896887</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>348.92037187089284</c:v>
+                  <c:v>348.87658976517741</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>366.42697665235454</c:v>
+                  <c:v>366.38319454663912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18086,7 +18216,7 @@
                   <c:v>42853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42886</c:v>
+                  <c:v>46080</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>42916</c:v>
@@ -18413,319 +18543,319 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3782105715432965E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.7167320074873662E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57959897679041683</c:v>
+                  <c:v>0.53243165671554316</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.702786265389312</c:v>
+                  <c:v>7.6556189453144388</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.866813639893314</c:v>
+                  <c:v>13.819646319818441</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15.066723050895511</c:v>
+                  <c:v>15.019555730820638</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>14.878099706928005</c:v>
+                  <c:v>14.830932386853132</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>16.591992506617576</c:v>
+                  <c:v>16.544825186542703</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.913234124359064</c:v>
+                  <c:v>40.866066804284195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46.351629978355263</c:v>
+                  <c:v>46.304462658280386</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>54.934667542692608</c:v>
+                  <c:v>54.887500222617739</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>88.041732973627546</c:v>
+                  <c:v>87.994565653552684</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>157.37105286259222</c:v>
+                  <c:v>157.32388554251733</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>222.12126229009593</c:v>
+                  <c:v>222.07409497002104</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>246.03684008077505</c:v>
+                  <c:v>245.98967276070016</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>288.00540758373802</c:v>
+                  <c:v>287.95824026366319</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>361.42999729059869</c:v>
+                  <c:v>361.38282997052386</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>398.85880451809669</c:v>
+                  <c:v>398.8116371980218</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>383.26085077798257</c:v>
+                  <c:v>383.21368345790773</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>362.97348804728466</c:v>
+                  <c:v>362.92632072720983</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>370.11821683323473</c:v>
+                  <c:v>370.07104951315989</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>389.42688804439149</c:v>
+                  <c:v>389.3797207243166</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>402.98939610334662</c:v>
+                  <c:v>402.94222878327179</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>422.37345553914224</c:v>
+                  <c:v>422.32628821906735</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>418.14489541840015</c:v>
+                  <c:v>418.09772809832526</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>416.56731887978844</c:v>
+                  <c:v>416.52015155971355</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>443.03688796494799</c:v>
+                  <c:v>442.98972064487316</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>486.16990261094327</c:v>
+                  <c:v>486.12273529086843</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>498.005167388789</c:v>
+                  <c:v>497.95800006871411</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>498.90670154904672</c:v>
+                  <c:v>498.85953422897182</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>499.11365880948654</c:v>
+                  <c:v>499.06649148941165</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>499.19520733105378</c:v>
+                  <c:v>499.14804001097889</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>499.15743304036585</c:v>
+                  <c:v>499.11026572029095</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>499.88046098898616</c:v>
+                  <c:v>499.83329366891127</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>505.05099885998266</c:v>
+                  <c:v>505.00383153990776</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>508.21494193451935</c:v>
+                  <c:v>508.16777461444445</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>508.79682841510925</c:v>
+                  <c:v>508.74966109503436</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>509.51578528070536</c:v>
+                  <c:v>509.46861796063047</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>510.7754646513003</c:v>
+                  <c:v>510.72829733122541</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>511.3962796036538</c:v>
+                  <c:v>511.3491122835789</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>513.19080303179044</c:v>
+                  <c:v>513.14363571171555</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>513.4108061014947</c:v>
+                  <c:v>513.36363878141981</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>513.42176781265152</c:v>
+                  <c:v>513.37460049257663</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>513.43840767266863</c:v>
+                  <c:v>513.39124035259374</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>541.76085103878916</c:v>
+                  <c:v>541.71368371871426</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>548.31455391774386</c:v>
+                  <c:v>548.26738659766897</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>548.42358853725318</c:v>
+                  <c:v>548.3764212171784</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>549.25120419774407</c:v>
+                  <c:v>549.20403687766918</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>547.94264608550873</c:v>
+                  <c:v>547.89547876543384</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>548.77457534742291</c:v>
+                  <c:v>548.72740802734802</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>549.57964217181484</c:v>
+                  <c:v>549.53247485173995</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>563.79412403149411</c:v>
+                  <c:v>563.74695671141922</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>576.14629645503999</c:v>
+                  <c:v>576.0991291349651</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>579.4237932103814</c:v>
+                  <c:v>579.37662589030651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18773,7 +18903,7 @@
                   <c:v>42853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42886</c:v>
+                  <c:v>46080</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>42916</c:v>
@@ -19103,316 +19233,316 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.3852143594406969E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.3852143594407247E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.616300105620283E-2</c:v>
+                  <c:v>-1.9548215415643E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.2230273494020736E-2</c:v>
+                  <c:v>1.8845059134580566E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.2221396844962182</c:v>
+                  <c:v>1.2187544701367781</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0335163405287116</c:v>
+                  <c:v>1.0301311261692714</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.60387541546592516</c:v>
+                  <c:v>0.60049020110648499</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.13055788142748526</c:v>
+                  <c:v>-0.13394309578692543</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.34851583859460789</c:v>
+                  <c:v>-0.35190105295405516</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2.5582376885837235</c:v>
+                  <c:v>-2.5616229029431636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-4.2073925728337542</c:v>
+                  <c:v>-4.2107777871931944</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-14.929553614601446</c:v>
+                  <c:v>-14.932938828960914</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-6.8501424339173695</c:v>
+                  <c:v>-6.8535276482768381</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-17.263350045976779</c:v>
+                  <c:v>-17.266735260336247</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-12.332506966762821</c:v>
+                  <c:v>-12.335892181122233</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>58.106865896756005</c:v>
+                  <c:v>58.103480682396594</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>95.535673124254004</c:v>
+                  <c:v>95.532287909894535</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>79.937719384139882</c:v>
+                  <c:v>79.93433416978047</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>57.623215696043474</c:v>
+                  <c:v>57.619830481684062</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>63.682129354476388</c:v>
+                  <c:v>63.678744140116976</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>82.990800565633151</c:v>
+                  <c:v>82.987415351273683</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>96.553308624588283</c:v>
+                  <c:v>96.549923410228871</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>115.9373680603839</c:v>
+                  <c:v>115.93398284602443</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>111.70880793964182</c:v>
+                  <c:v>111.70542272528235</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>110.13123140103011</c:v>
+                  <c:v>110.12784618667064</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>136.60080048618966</c:v>
+                  <c:v>136.59741527183024</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>179.73381513218493</c:v>
+                  <c:v>179.73042991782552</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>191.56907991003067</c:v>
+                  <c:v>191.5656946956712</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>191.60600829280901</c:v>
+                  <c:v>191.60262307844954</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>191.68755681437625</c:v>
+                  <c:v>191.68417160001678</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>191.64978252368832</c:v>
+                  <c:v>191.64639730932885</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>191.59424384820642</c:v>
+                  <c:v>191.59085863384695</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>191.45096357006366</c:v>
+                  <c:v>191.4475783557042</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>191.76135846214714</c:v>
+                  <c:v>191.75797324778767</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>192.08593071262925</c:v>
+                  <c:v>192.08254549826978</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>192.00037206169367</c:v>
+                  <c:v>191.9969868473342</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>193.26005143228861</c:v>
+                  <c:v>193.25666621792914</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>193.8808663846421</c:v>
+                  <c:v>193.87748117028264</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>195.67538981277875</c:v>
+                  <c:v>195.67200459841928</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>195.67538981277869</c:v>
+                  <c:v>195.67200459841922</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>195.68100213063764</c:v>
+                  <c:v>195.67761691627817</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>195.680619109389</c:v>
+                  <c:v>195.67723389502953</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>195.63352487675371</c:v>
+                  <c:v>195.63013966239424</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>201.96288805777994</c:v>
+                  <c:v>201.95950284342047</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>201.99238041098755</c:v>
+                  <c:v>201.9889951966282</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>202.81999607147844</c:v>
+                  <c:v>202.81661085711897</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>200.78506788769289</c:v>
+                  <c:v>200.78168267333342</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>200.93568168273862</c:v>
+                  <c:v>200.93229646837915</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>200.659270300922</c:v>
+                  <c:v>200.65588508656253</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>197.36714737913957</c:v>
+                  <c:v>197.3637621647801</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>209.71931980268545</c:v>
+                  <c:v>209.71593458832598</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>212.99681655802686</c:v>
+                  <c:v>212.9934313436674</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19434,11 +19564,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="582118784"/>
-        <c:axId val="582317184"/>
+        <c:axId val="498043904"/>
+        <c:axId val="498053888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="582118784"/>
+        <c:axId val="498043904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19481,14 +19611,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="582317184"/>
+        <c:crossAx val="498053888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="582317184"/>
+        <c:axId val="498053888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19537,7 +19667,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="582118784"/>
+        <c:crossAx val="498043904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -19645,7 +19775,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19688,7 +19818,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19731,7 +19861,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19774,7 +19904,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19817,7 +19947,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19860,7 +19990,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19903,7 +20033,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19946,7 +20076,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20259,7 +20389,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20294,37 +20424,37 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="M1" s="12"/>
     </row>
@@ -20350,7 +20480,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -20401,28 +20531,28 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="Q4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="R4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="V4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="X4" s="6">
         <v>43098</v>
@@ -24775,6 +24905,41 @@
         <v>2352.4309798958438</v>
       </c>
       <c r="K109" s="21">
+        <v>7246.1850032321172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4893.7540233362733</v>
+      </c>
+      <c r="I110" s="22">
+        <v>7246.1850032321172</v>
+      </c>
+      <c r="J110" s="22">
+        <v>2352.4309798958438</v>
+      </c>
+      <c r="K110" s="21">
         <v>7246.1850032321172</v>
       </c>
     </row>
@@ -24793,8 +24958,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH109"/>
+  <sheetPr codeName="Sheet2">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24829,49 +24996,49 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="14" t="s">
-        <v>11</v>
-      </c>
       <c r="L1" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -24896,12 +25063,12 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
         <f>MIN(F:F)</f>
-        <v>0</v>
+        <v>-145.08939735614592</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="4"/>
@@ -24957,28 +25124,28 @@
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -30590,6 +30757,53 @@
         <v>73.035028220618088</v>
       </c>
       <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>-379.02549223852623</v>
+      </c>
+      <c r="E110" s="22">
+        <v>-150.16858274017764</v>
+      </c>
+      <c r="F110" s="22">
+        <v>-145.08939735614592</v>
+      </c>
+      <c r="G110" s="22">
+        <v>-366.20562868767797</v>
+      </c>
+      <c r="H110" s="22">
+        <v>6052.5924500756464</v>
+      </c>
+      <c r="I110" s="22">
+        <v>11584.987800428717</v>
+      </c>
+      <c r="J110" s="22">
+        <v>5532.3953503530702</v>
+      </c>
+      <c r="K110" s="21">
+        <v>11951.193429116394</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -30611,7 +30825,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30646,52 +30860,52 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="14" t="s">
-        <v>32</v>
-      </c>
       <c r="P1" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -30716,7 +30930,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -30781,28 +30995,28 @@
         <v>0.95</v>
       </c>
       <c r="Q4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -36686,6 +36900,56 @@
         <v>78.982013449904031</v>
       </c>
       <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4478.5830960357953</v>
+      </c>
+      <c r="I110" s="22">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="J110" s="22">
+        <v>2256.7315129624458</v>
+      </c>
+      <c r="K110" s="21">
+        <v>6735.3146089982411</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -36707,7 +36971,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36747,43 +37011,43 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="L1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="M1" s="14" t="s">
         <v>10</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="O1" s="12"/>
     </row>
@@ -36813,7 +37077,7 @@
         <v>1550</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
@@ -36870,28 +37134,28 @@
       </c>
       <c r="N4" s="7"/>
       <c r="Q4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -41874,6 +42138,47 @@
         <v>901.75787582245493</v>
       </c>
       <c r="M109" s="21">
+        <v>3181.8326442193757</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="20">
+        <v>665022</v>
+      </c>
+      <c r="E110" s="20">
+        <v>1877770.3918344665</v>
+      </c>
+      <c r="F110" s="21">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22">
+        <v>2280.0747683969207</v>
+      </c>
+      <c r="K110" s="22">
+        <v>3181.8326442193757</v>
+      </c>
+      <c r="L110" s="22">
+        <v>901.75787582245493</v>
+      </c>
+      <c r="M110" s="21">
         <v>3181.8326442193757</v>
       </c>
     </row>
@@ -41895,7 +42200,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41930,37 +42235,37 @@
   <sheetData>
     <row r="1" spans="1:32" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>2</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="M1" s="12"/>
     </row>
@@ -41986,7 +42291,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -42037,28 +42342,28 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="Q4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="R4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="V4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="X4" s="6">
         <v>43098</v>
@@ -46411,6 +46716,41 @@
         <v>461.2250703448251</v>
       </c>
       <c r="K109" s="21">
+        <v>1243.9035388429725</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1243.9035388429725</v>
+      </c>
+      <c r="J110" s="22">
+        <v>461.2250703448251</v>
+      </c>
+      <c r="K110" s="21">
         <v>1243.9035388429725</v>
       </c>
     </row>
@@ -46432,7 +46772,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -46467,49 +46807,49 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -46534,7 +46874,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -46595,28 +46935,28 @@
       <c r="O4" s="27"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -52228,6 +52568,53 @@
         <v>73.035028220618088</v>
       </c>
       <c r="O109" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="21">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J110" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L110" s="26">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="M110" s="27">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N110" s="27">
+        <v>67.892638468724456</v>
+      </c>
+      <c r="O110" s="27">
         <v>0.2</v>
       </c>
     </row>
@@ -52249,7 +52636,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -52284,52 +52671,52 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -52354,7 +52741,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -52419,28 +52806,28 @@
         <v>0.95</v>
       </c>
       <c r="Q4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
@@ -58323,6 +58710,56 @@
         <v>78.982013449904031</v>
       </c>
       <c r="P109" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="12.75">
+      <c r="A110" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.3013370512393063</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I110" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J110" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K110" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L110" s="26">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="M110" s="27">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="N110" s="27">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="O110" s="27">
+        <v>80.088128126201894</v>
+      </c>
+      <c r="P110" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -58384,43 +58821,43 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="L1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="M1" s="14" t="s">
         <v>10</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="O1" s="12"/>
     </row>
@@ -58450,7 +58887,7 @@
         <v>1550</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
@@ -58507,96 +58944,96 @@
       </c>
       <c r="N4" s="7"/>
       <c r="Q4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="S4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="T4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="V4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="W4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="X4" s="32" t="s">
         <v>18</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>19</v>
       </c>
       <c r="Z4" s="6">
         <v>43098</v>
       </c>
       <c r="AA4" s="7">
         <f>VLOOKUP(Z4,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AB4" s="7">
         <f t="shared" ref="AB4:AB5" si="0">0-AA4</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AC4" s="6">
         <v>43098</v>
       </c>
       <c r="AD4" s="1">
         <f>VLOOKUP(AC4,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AE4" s="1">
         <f t="shared" ref="AE4" si="1">0-AD4</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AF4" s="6">
         <v>43098</v>
       </c>
       <c r="AG4" s="7">
         <f>VLOOKUP(AF4,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AH4" s="7">
         <f t="shared" ref="AH4:AH7" si="2">0-AG4</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="14.1" customHeight="1">
       <c r="A5" s="15">
-        <v>42886</v>
+        <v>46080</v>
       </c>
       <c r="B5" s="25">
-        <v>0.97</v>
+        <v>2.5239999294281006</v>
       </c>
       <c r="C5" s="20">
-        <v>0.99024999999999985</v>
+        <v>1.3013370512393063</v>
       </c>
       <c r="D5" s="20">
-        <v>143931</v>
+        <v>665022</v>
       </c>
       <c r="E5" s="20">
-        <v>2089485.9285714286</v>
+        <v>1877770.3918344665</v>
       </c>
       <c r="F5" s="21">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="22">
-        <v>4.5136191459209246E-2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="22">
-        <v>4.5136191459209246E-2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="22">
         <v>0</v>
@@ -58609,58 +59046,58 @@
         <v>43098</v>
       </c>
       <c r="R5" s="10">
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="S5" s="5">
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="T5" s="5">
-        <v>0.57959897679041683</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="U5" s="5">
-        <v>3.3852143594407247E-3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="5">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="W5" s="9">
-        <v>5.8749279870701368E-3</v>
+        <v>0</v>
       </c>
       <c r="X5" s="9">
-        <v>5.8749279870701368E-3</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="6">
         <v>43462</v>
       </c>
       <c r="AA5" s="7">
         <f>VLOOKUP(Z5,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AB5" s="7">
         <f t="shared" si="0"/>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AC5" s="6">
         <v>43462</v>
       </c>
       <c r="AD5" s="1">
         <f>VLOOKUP(AC5,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AE5" s="1">
         <f t="shared" ref="AE5:AE6" si="3">0-AD5</f>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AF5" s="6">
         <v>43462</v>
       </c>
       <c r="AG5" s="7">
         <f>VLOOKUP(AF5,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AH5" s="7">
         <f t="shared" si="2"/>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="14.1" customHeight="1">
@@ -58680,10 +59117,10 @@
         <v>1521948.92</v>
       </c>
       <c r="F6" s="21">
-        <v>-4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="22">
-        <v>-4.5136191459209246E-2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
@@ -58692,47 +59129,47 @@
         <v>0</v>
       </c>
       <c r="J6" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M6" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="7"/>
       <c r="Q6" s="6">
         <v>43462</v>
       </c>
       <c r="R6" s="10">
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="S6" s="5">
-        <v>263.30019012675183</v>
+        <v>263.25640802103641</v>
       </c>
       <c r="T6" s="5">
-        <v>246.03684008077505</v>
+        <v>245.98967276070016</v>
       </c>
       <c r="U6" s="5">
-        <v>-17.263350045976779</v>
+        <v>-17.266735260336247</v>
       </c>
       <c r="V6" s="5">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="W6" s="9">
-        <v>-6.556527755512162E-2</v>
+        <v>-6.558904070041284E-2</v>
       </c>
       <c r="X6" s="9">
-        <v>-6.5431454731200711E-2</v>
+        <v>-6.5465305989182543E-2</v>
       </c>
       <c r="Z6" s="6">
         <v>43462</v>
       </c>
       <c r="AB6" s="7">
-        <v>246.03684008077505</v>
+        <v>245.98967276070016</v>
       </c>
       <c r="AC6" s="6">
         <v>43830</v>
@@ -58786,16 +59223,16 @@
         <v>0</v>
       </c>
       <c r="J7" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="7"/>
       <c r="Q7" s="6">
@@ -58805,32 +59242,32 @@
         <v>43.135897352006509</v>
       </c>
       <c r="S7" s="5">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="T7" s="5">
-        <v>443.03688796494799</v>
+        <v>442.98972064487316</v>
       </c>
       <c r="U7" s="5">
-        <v>136.60080048618966</v>
+        <v>136.59741527183024</v>
       </c>
       <c r="V7" s="5">
-        <v>103.29053972594444</v>
+        <v>103.24337240586956</v>
       </c>
       <c r="W7" s="9">
-        <v>0.44577256422404427</v>
+        <v>0.4458252145252744</v>
       </c>
       <c r="X7" s="9">
-        <v>0.21756075338951386</v>
+        <v>0.21760724296498135</v>
       </c>
       <c r="AB7" s="8">
         <f>IRR(AB4:AB6)</f>
-        <v>-6.5431454731200711E-2</v>
+        <v>-6.5465305989182543E-2</v>
       </c>
       <c r="AC7" s="6">
         <v>43830</v>
       </c>
       <c r="AE7" s="1">
-        <v>443.03688796494799</v>
+        <v>442.98972064487316</v>
       </c>
       <c r="AF7" s="6">
         <v>44196</v>
@@ -58873,16 +59310,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="7"/>
       <c r="Q8" s="6">
@@ -58892,32 +59329,32 @@
         <v>0</v>
       </c>
       <c r="S8" s="5">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="T8" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="U8" s="5">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="V8" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="W8" s="9">
-        <v>0.62515182688236726</v>
+        <v>0.62523010968710047</v>
       </c>
       <c r="X8" s="9">
-        <v>0.18427566897698489</v>
+        <v>0.18430783116175009</v>
       </c>
       <c r="AE8" s="2">
         <f>IRR(AE4:AE7)</f>
-        <v>0.21756075338951386</v>
+        <v>0.21760724296498135</v>
       </c>
       <c r="AF8" s="6">
         <v>44196</v>
       </c>
       <c r="AH8" s="7">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="14.1" customHeight="1">
@@ -58949,16 +59386,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M9" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="7"/>
       <c r="Q9" s="29">
@@ -58968,26 +59405,26 @@
         <v>0</v>
       </c>
       <c r="S9" s="5">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="T9" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="U9" s="5">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="V9" s="5">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="W9" s="9">
-        <v>0.62515182688236726</v>
+        <v>0.62523010968710047</v>
       </c>
       <c r="X9" s="9">
-        <v>0.13374077680861762</v>
+        <v>0.13376124558787272</v>
       </c>
       <c r="AH9" s="2">
         <f>IRR(AH4:AH8)</f>
-        <v>0.18427566897698489</v>
+        <v>0.18430783116175009</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="14.1" customHeight="1">
@@ -59019,16 +59456,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="7"/>
       <c r="Q10" s="29">
@@ -59038,44 +59475,44 @@
         <v>11.079325740253353</v>
       </c>
       <c r="S10" s="5">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="T10" s="5">
-        <v>509.51578528070536</v>
+        <v>509.46861796063047</v>
       </c>
       <c r="U10" s="5">
-        <v>192.00037206169367</v>
+        <v>191.9969868473342</v>
       </c>
       <c r="V10" s="5">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
       <c r="W10" s="9">
-        <v>0.60469622597268413</v>
+        <v>0.60476895580889278</v>
       </c>
       <c r="X10" s="9">
-        <v>0.10458712586200214</v>
+        <v>0.1046018033933096</v>
       </c>
       <c r="Z10" s="6">
         <v>43098</v>
       </c>
       <c r="AA10" s="7">
         <f>VLOOKUP(Z10,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AB10" s="1">
         <f>-AA10</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AC10" s="6">
         <v>43098</v>
       </c>
       <c r="AD10" s="1">
         <f t="shared" ref="AD10:AD15" si="4">VLOOKUP(AC10,Q:R,2,)</f>
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="AE10" s="1">
         <f t="shared" ref="AE10:AE15" si="5">-AD10</f>
-        <v>-0.57621376243097611</v>
+        <v>-0.53243165671554316</v>
       </c>
       <c r="AF10" s="6">
         <v>43098</v>
@@ -59117,16 +59554,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="22">
-        <v>4.3782105715432965E-2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="22">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="22">
-        <v>3.3852143594406969E-3</v>
+        <v>0</v>
       </c>
       <c r="M11" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="7"/>
       <c r="Q11" s="29">
@@ -59136,19 +59573,19 @@
         <v>0.24237534426794127</v>
       </c>
       <c r="S11" s="5">
-        <v>317.75778856327963</v>
+        <v>317.71400645756421</v>
       </c>
       <c r="T11" s="5">
-        <v>513.43840767266863</v>
+        <v>513.39124035259374</v>
       </c>
       <c r="U11" s="5">
-        <v>195.680619109389</v>
+        <v>195.67723389502953</v>
       </c>
       <c r="V11" s="5">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="W11" s="9">
-        <v>0.61581690882903517</v>
+        <v>0.61589111565078369</v>
       </c>
       <c r="X11" s="9">
         <v>8.7073790790229921E-2</v>
@@ -59158,22 +59595,22 @@
       </c>
       <c r="AA11" s="7">
         <f>VLOOKUP(Z11,Q:R,2,)</f>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AB11" s="1">
         <f>-AA11</f>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AC11" s="6">
         <v>43462</v>
       </c>
       <c r="AD11" s="1">
         <f t="shared" si="4"/>
-        <v>262.72397636432083</v>
+        <v>262.72397636432089</v>
       </c>
       <c r="AE11" s="1">
         <f t="shared" si="5"/>
-        <v>-262.72397636432083</v>
+        <v>-262.72397636432089</v>
       </c>
       <c r="AF11" s="6">
         <v>43462</v>
@@ -59215,16 +59652,16 @@
         <v>0.53243165671554316</v>
       </c>
       <c r="J12" s="22">
-        <v>0.57621376243097611</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="K12" s="22">
-        <v>0.57959897679041683</v>
+        <v>0.53243165671554316</v>
       </c>
       <c r="L12" s="22">
-        <v>3.3852143594407247E-3</v>
+        <v>0</v>
       </c>
       <c r="M12" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="7"/>
       <c r="Q12" s="29">
@@ -59234,19 +59671,19 @@
         <v>48.669188089074908</v>
       </c>
       <c r="S12" s="5">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="T12" s="5">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="U12" s="5">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="V12" s="5">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="W12" s="9">
-        <v>0.58128039180943369</v>
+        <v>0.58134061418189364</v>
       </c>
       <c r="X12" s="9">
         <v>7.7879086338844994E-2</v>
@@ -59313,16 +59750,16 @@
         <v>7.6556189453144388</v>
       </c>
       <c r="J13" s="22">
-        <v>7.7189492664455148</v>
+        <v>7.6751671607300818</v>
       </c>
       <c r="K13" s="22">
-        <v>7.702786265389312</v>
+        <v>7.6556189453144388</v>
       </c>
       <c r="L13" s="22">
-        <v>-1.616300105620283E-2</v>
+        <v>-1.9548215415643E-2</v>
       </c>
       <c r="M13" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="7"/>
       <c r="Z13" s="6">
@@ -59387,16 +59824,16 @@
         <v>13.819646319818441</v>
       </c>
       <c r="J14" s="22">
-        <v>13.844583366399293</v>
+        <v>13.80080126068386</v>
       </c>
       <c r="K14" s="22">
-        <v>13.866813639893314</v>
+        <v>13.819646319818441</v>
       </c>
       <c r="L14" s="22">
-        <v>2.2230273494020736E-2</v>
+        <v>1.8845059134580566E-2</v>
       </c>
       <c r="M14" s="21">
-        <v>4.7167320074873662E-2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="7"/>
       <c r="Z14" s="29">
@@ -59461,23 +59898,23 @@
         <v>8.2164328632246892</v>
       </c>
       <c r="J15" s="22">
-        <v>13.844583366399293</v>
+        <v>13.80080126068386</v>
       </c>
       <c r="K15" s="22">
-        <v>15.066723050895511</v>
+        <v>15.019555730820638</v>
       </c>
       <c r="L15" s="22">
-        <v>1.2221396844962182</v>
+        <v>1.2187544701367781</v>
       </c>
       <c r="M15" s="21">
-        <v>6.8502901876708231</v>
+        <v>6.8031228675959499</v>
       </c>
       <c r="N15" s="7"/>
       <c r="Z15" s="29">
         <v>44561</v>
       </c>
       <c r="AB15" s="7">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="AC15" s="29">
         <v>44925</v>
@@ -59530,27 +59967,27 @@
         <v>7.4940646601115359</v>
       </c>
       <c r="J16" s="22">
-        <v>13.844583366399293</v>
+        <v>13.80080126068386</v>
       </c>
       <c r="K16" s="22">
-        <v>14.878099706928005</v>
+        <v>14.830932386853132</v>
       </c>
       <c r="L16" s="22">
-        <v>1.0335163405287116</v>
+        <v>1.0301311261692714</v>
       </c>
       <c r="M16" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N16" s="7"/>
       <c r="AB16" s="2">
         <f>IRR(AB10:AB15)</f>
-        <v>0.13374077680861762</v>
+        <v>0.13376124558787272</v>
       </c>
       <c r="AC16" s="29">
         <v>44925</v>
       </c>
       <c r="AE16" s="1">
-        <v>509.51578528070536</v>
+        <v>509.46861796063047</v>
       </c>
       <c r="AF16" s="29">
         <v>45289</v>
@@ -59592,21 +60029,21 @@
         <v>9.2079574598011078</v>
       </c>
       <c r="J17" s="22">
-        <v>15.988117091151651</v>
+        <v>15.944334985436218</v>
       </c>
       <c r="K17" s="22">
-        <v>16.591992506617576</v>
+        <v>16.544825186542703</v>
       </c>
       <c r="L17" s="22">
-        <v>0.60387541546592516</v>
+        <v>0.60049020110648499</v>
       </c>
       <c r="M17" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N17" s="7"/>
       <c r="AE17" s="2">
         <f>IRR(AE10:AE16)</f>
-        <v>0.10458712586200214</v>
+        <v>0.1046018033933096</v>
       </c>
       <c r="AF17" s="29">
         <v>45289</v>
@@ -59644,16 +60081,16 @@
         <v>33.5291990775426</v>
       </c>
       <c r="J18" s="22">
-        <v>41.04379200578655</v>
+        <v>41.00000990007112</v>
       </c>
       <c r="K18" s="22">
-        <v>40.913234124359064</v>
+        <v>40.866066804284195</v>
       </c>
       <c r="L18" s="22">
-        <v>-0.13055788142748526</v>
+        <v>-0.13394309578692543</v>
       </c>
       <c r="M18" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N18" s="7"/>
       <c r="AH18" s="2">
@@ -59690,16 +60127,16 @@
         <v>38.967594931538791</v>
       </c>
       <c r="J19" s="22">
-        <v>46.70014581694987</v>
+        <v>46.656363711234441</v>
       </c>
       <c r="K19" s="22">
-        <v>46.351629978355263</v>
+        <v>46.304462658280386</v>
       </c>
       <c r="L19" s="22">
-        <v>-0.34851583859460789</v>
+        <v>-0.35190105295405516</v>
       </c>
       <c r="M19" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N19" s="7"/>
       <c r="Z19" s="6">
@@ -59742,16 +60179,16 @@
         <v>47.550632495876144</v>
       </c>
       <c r="J20" s="22">
-        <v>57.492905231276332</v>
+        <v>57.449123125560902</v>
       </c>
       <c r="K20" s="22">
-        <v>54.934667542692608</v>
+        <v>54.887500222617739</v>
       </c>
       <c r="L20" s="22">
-        <v>-2.5582376885837235</v>
+        <v>-2.5616229029431636</v>
       </c>
       <c r="M20" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N20" s="7"/>
       <c r="Z20" s="6">
@@ -59794,16 +60231,16 @@
         <v>80.657697926811082</v>
       </c>
       <c r="J21" s="22">
-        <v>92.2491255464613</v>
+        <v>92.205343440745878</v>
       </c>
       <c r="K21" s="22">
-        <v>88.041732973627546</v>
+        <v>87.994565653552684</v>
       </c>
       <c r="L21" s="22">
-        <v>-4.2073925728337542</v>
+        <v>-4.2107777871931944</v>
       </c>
       <c r="M21" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N21" s="8"/>
       <c r="Z21" s="6">
@@ -59846,16 +60283,16 @@
         <v>149.98701781577574</v>
       </c>
       <c r="J22" s="22">
-        <v>172.30060647719367</v>
+        <v>172.25682437147825</v>
       </c>
       <c r="K22" s="22">
-        <v>157.37105286259222</v>
+        <v>157.32388554251733</v>
       </c>
       <c r="L22" s="22">
-        <v>-14.929553614601446</v>
+        <v>-14.932938828960914</v>
       </c>
       <c r="M22" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N22" s="7"/>
       <c r="Z22" s="6">
@@ -59898,16 +60335,16 @@
         <v>214.73722724327945</v>
       </c>
       <c r="J23" s="22">
-        <v>228.9714047240133</v>
+        <v>228.92762261829787</v>
       </c>
       <c r="K23" s="22">
-        <v>222.12126229009593</v>
+        <v>222.07409497002104</v>
       </c>
       <c r="L23" s="22">
-        <v>-6.8501424339173695</v>
+        <v>-6.8535276482768381</v>
       </c>
       <c r="M23" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N23" s="7"/>
       <c r="Z23" s="29">
@@ -59950,16 +60387,16 @@
         <v>238.65280503395857</v>
       </c>
       <c r="J24" s="22">
-        <v>263.30019012675183</v>
+        <v>263.25640802103641</v>
       </c>
       <c r="K24" s="22">
-        <v>246.03684008077505</v>
+        <v>245.98967276070016</v>
       </c>
       <c r="L24" s="22">
-        <v>-17.263350045976779</v>
+        <v>-17.266735260336247</v>
       </c>
       <c r="M24" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N24" s="7"/>
       <c r="Q24" s="3"/>
@@ -60003,16 +60440,16 @@
         <v>280.62137253692157</v>
       </c>
       <c r="J25" s="22">
-        <v>300.33791455050084</v>
+        <v>300.29413244478542</v>
       </c>
       <c r="K25" s="22">
-        <v>288.00540758373802</v>
+        <v>287.95824026366319</v>
       </c>
       <c r="L25" s="22">
-        <v>-12.332506966762821</v>
+        <v>-12.335892181122233</v>
       </c>
       <c r="M25" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N25" s="7"/>
       <c r="Z25" s="29">
@@ -60055,16 +60492,16 @@
         <v>354.04596224378224</v>
       </c>
       <c r="J26" s="22">
-        <v>303.32313139384269</v>
+        <v>303.27934928812726</v>
       </c>
       <c r="K26" s="22">
-        <v>361.42999729059869</v>
+        <v>361.38282997052386</v>
       </c>
       <c r="L26" s="22">
-        <v>58.106865896756005</v>
+        <v>58.103480682396594</v>
       </c>
       <c r="M26" s="21">
-        <v>7.3840350468164679</v>
+        <v>7.3368677267415947</v>
       </c>
       <c r="N26" s="7"/>
       <c r="Z26" s="29">
@@ -60107,16 +60544,16 @@
         <v>363.36142235493008</v>
       </c>
       <c r="J27" s="22">
-        <v>303.32313139384269</v>
+        <v>303.27934928812726</v>
       </c>
       <c r="K27" s="22">
-        <v>398.85880451809669</v>
+        <v>398.8116371980218</v>
       </c>
       <c r="L27" s="22">
-        <v>95.535673124254004</v>
+        <v>95.532287909894535</v>
       </c>
       <c r="M27" s="21">
-        <v>35.497382163166584</v>
+        <v>35.450214843091715</v>
       </c>
       <c r="N27" s="7"/>
       <c r="Z27" s="29">
@@ -60155,16 +60592,16 @@
         <v>347.46870028607333</v>
       </c>
       <c r="J28" s="22">
-        <v>303.32313139384269</v>
+        <v>303.27934928812726</v>
       </c>
       <c r="K28" s="22">
-        <v>383.26085077798257</v>
+        <v>383.21368345790773</v>
       </c>
       <c r="L28" s="22">
-        <v>79.937719384139882</v>
+        <v>79.93433416978047</v>
       </c>
       <c r="M28" s="21">
-        <v>35.792150491909254</v>
+        <v>35.744983171834384</v>
       </c>
       <c r="N28" s="7"/>
       <c r="AB28" s="2">
@@ -60201,16 +60638,16 @@
         <v>327.18133755537542</v>
       </c>
       <c r="J29" s="22">
-        <v>305.35027235124119</v>
+        <v>305.30649024552577</v>
       </c>
       <c r="K29" s="22">
-        <v>362.97348804728466</v>
+        <v>362.92632072720983</v>
       </c>
       <c r="L29" s="22">
-        <v>57.623215696043474</v>
+        <v>57.619830481684062</v>
       </c>
       <c r="M29" s="21">
-        <v>35.792150491909254</v>
+        <v>35.744983171834384</v>
       </c>
       <c r="N29" s="7"/>
     </row>
@@ -60243,16 +60680,16 @@
         <v>334.32606634132549</v>
       </c>
       <c r="J30" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K30" s="22">
-        <v>370.11821683323473</v>
+        <v>370.07104951315989</v>
       </c>
       <c r="L30" s="22">
-        <v>63.682129354476388</v>
+        <v>63.678744140116976</v>
       </c>
       <c r="M30" s="21">
-        <v>35.792150491909254</v>
+        <v>35.744983171834384</v>
       </c>
       <c r="N30" s="7"/>
     </row>
@@ -60285,16 +60722,16 @@
         <v>352.98211763964912</v>
       </c>
       <c r="J31" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K31" s="22">
-        <v>389.42688804439149</v>
+        <v>389.3797207243166</v>
       </c>
       <c r="L31" s="22">
-        <v>82.990800565633151</v>
+        <v>82.987415351273683</v>
       </c>
       <c r="M31" s="21">
-        <v>36.444770404742378</v>
+        <v>36.397603084667509</v>
       </c>
       <c r="N31" s="7"/>
     </row>
@@ -60327,16 +60764,16 @@
         <v>355.48980429575056</v>
       </c>
       <c r="J32" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K32" s="22">
-        <v>402.98939610334662</v>
+        <v>402.94222878327179</v>
       </c>
       <c r="L32" s="22">
-        <v>96.553308624588283</v>
+        <v>96.549923410228871</v>
       </c>
       <c r="M32" s="21">
-        <v>47.49959180759609</v>
+        <v>47.45242448752122</v>
       </c>
       <c r="N32" s="7"/>
     </row>
@@ -60369,16 +60806,16 @@
         <v>352.2715854433639</v>
       </c>
       <c r="J33" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K33" s="22">
-        <v>422.37345553914224</v>
+        <v>422.32628821906735</v>
       </c>
       <c r="L33" s="22">
-        <v>115.9373680603839</v>
+        <v>115.93398284602443</v>
       </c>
       <c r="M33" s="21">
-        <v>70.101870095778324</v>
+        <v>70.054702775703447</v>
       </c>
       <c r="N33" s="7"/>
     </row>
@@ -60411,16 +60848,16 @@
         <v>337.60137926289644</v>
       </c>
       <c r="J34" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K34" s="22">
-        <v>418.14489541840015</v>
+        <v>418.09772809832526</v>
       </c>
       <c r="L34" s="22">
-        <v>111.70880793964182</v>
+        <v>111.70542272528235</v>
       </c>
       <c r="M34" s="21">
-        <v>80.54351615550371</v>
+        <v>80.496348835428833</v>
       </c>
       <c r="N34" s="7"/>
     </row>
@@ -60453,16 +60890,16 @@
         <v>331.64813030229362</v>
       </c>
       <c r="J35" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K35" s="22">
-        <v>416.56731887978844</v>
+        <v>416.52015155971355</v>
       </c>
       <c r="L35" s="22">
-        <v>110.13123140103011</v>
+        <v>110.12784618667064</v>
       </c>
       <c r="M35" s="21">
-        <v>84.919188577494822</v>
+        <v>84.872021257419945</v>
       </c>
       <c r="N35" s="7"/>
     </row>
@@ -60495,16 +60932,16 @@
         <v>339.74634823900357</v>
       </c>
       <c r="J36" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K36" s="22">
-        <v>443.03688796494799</v>
+        <v>442.98972064487316</v>
       </c>
       <c r="L36" s="22">
-        <v>136.60080048618966</v>
+        <v>136.59741527183024</v>
       </c>
       <c r="M36" s="21">
-        <v>103.29053972594444</v>
+        <v>103.24337240586956</v>
       </c>
       <c r="N36" s="7"/>
       <c r="Q36" s="3"/>
@@ -60538,16 +60975,16 @@
         <v>126.76448886023145</v>
       </c>
       <c r="J37" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K37" s="22">
-        <v>486.16990261094327</v>
+        <v>486.12273529086843</v>
       </c>
       <c r="L37" s="22">
-        <v>179.73381513218493</v>
+        <v>179.73042991782552</v>
       </c>
       <c r="M37" s="21">
-        <v>359.40541375071183</v>
+        <v>359.358246430637</v>
       </c>
       <c r="N37" s="7"/>
     </row>
@@ -60580,16 +61017,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K38" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L38" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M38" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N38" s="7"/>
     </row>
@@ -60622,16 +61059,16 @@
         <v>0</v>
       </c>
       <c r="J39" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K39" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L39" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M39" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N39" s="7"/>
     </row>
@@ -60664,16 +61101,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K40" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L40" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M40" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N40" s="7"/>
     </row>
@@ -60706,16 +61143,16 @@
         <v>0</v>
       </c>
       <c r="J41" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K41" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L41" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M41" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N41" s="7"/>
     </row>
@@ -60748,16 +61185,16 @@
         <v>0</v>
       </c>
       <c r="J42" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K42" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L42" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M42" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N42" s="7"/>
     </row>
@@ -60790,16 +61227,16 @@
         <v>0</v>
       </c>
       <c r="J43" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K43" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L43" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M43" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N43" s="7"/>
     </row>
@@ -60832,16 +61269,16 @@
         <v>0</v>
       </c>
       <c r="J44" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K44" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L44" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M44" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N44" s="7"/>
     </row>
@@ -60874,16 +61311,16 @@
         <v>0</v>
       </c>
       <c r="J45" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K45" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L45" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M45" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N45" s="7"/>
     </row>
@@ -60916,16 +61353,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K46" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L46" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M46" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N46" s="7"/>
     </row>
@@ -60958,16 +61395,16 @@
         <v>0</v>
       </c>
       <c r="J47" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K47" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L47" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M47" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N47" s="7"/>
     </row>
@@ -61000,16 +61437,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K48" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L48" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M48" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="N48" s="7"/>
     </row>
@@ -61042,16 +61479,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K49" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L49" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M49" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="14.1" customHeight="1">
@@ -61083,16 +61520,16 @@
         <v>0</v>
       </c>
       <c r="J50" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K50" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L50" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M50" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="14.1" customHeight="1">
@@ -61124,16 +61561,16 @@
         <v>0</v>
       </c>
       <c r="J51" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K51" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L51" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M51" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="14.1" customHeight="1">
@@ -61165,16 +61602,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K52" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L52" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M52" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="14.1" customHeight="1">
@@ -61206,16 +61643,16 @@
         <v>0</v>
       </c>
       <c r="J53" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K53" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L53" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M53" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="14.1" customHeight="1">
@@ -61247,16 +61684,16 @@
         <v>0</v>
       </c>
       <c r="J54" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K54" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L54" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M54" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="14.1" customHeight="1">
@@ -61288,16 +61725,16 @@
         <v>0</v>
       </c>
       <c r="J55" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K55" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L55" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M55" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="14.1" customHeight="1">
@@ -61329,16 +61766,16 @@
         <v>0</v>
       </c>
       <c r="J56" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K56" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L56" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M56" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="14.1" customHeight="1">
@@ -61370,16 +61807,16 @@
         <v>0</v>
       </c>
       <c r="J57" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K57" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L57" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M57" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="14.1" customHeight="1">
@@ -61411,16 +61848,16 @@
         <v>0</v>
       </c>
       <c r="J58" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K58" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L58" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M58" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="14.1" customHeight="1">
@@ -61452,16 +61889,16 @@
         <v>0</v>
       </c>
       <c r="J59" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K59" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L59" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M59" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="14.1" customHeight="1">
@@ -61493,16 +61930,16 @@
         <v>0</v>
       </c>
       <c r="J60" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K60" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L60" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M60" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="14.1" customHeight="1">
@@ -61534,16 +61971,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K61" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L61" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M61" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="14.1" customHeight="1">
@@ -61575,16 +62012,16 @@
         <v>0</v>
       </c>
       <c r="J62" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K62" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L62" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M62" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="14.1" customHeight="1">
@@ -61616,16 +62053,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="22">
-        <v>306.43608747875834</v>
+        <v>306.39230537304292</v>
       </c>
       <c r="K63" s="22">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
       <c r="L63" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M63" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="14.1" customHeight="1">
@@ -61657,16 +62094,16 @@
         <v>0.90153416025771216</v>
       </c>
       <c r="J64" s="22">
-        <v>307.33762163901605</v>
+        <v>307.29383953330063</v>
       </c>
       <c r="K64" s="22">
-        <v>498.90670154904672</v>
+        <v>498.85953422897182</v>
       </c>
       <c r="L64" s="22">
-        <v>191.56907991003067</v>
+        <v>191.5656946956712</v>
       </c>
       <c r="M64" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="14.1" customHeight="1">
@@ -61698,16 +62135,16 @@
         <v>1.1084914206975303</v>
       </c>
       <c r="J65" s="22">
-        <v>307.50765051667753</v>
+        <v>307.46386841096211</v>
       </c>
       <c r="K65" s="22">
-        <v>499.11365880948654</v>
+        <v>499.06649148941165</v>
       </c>
       <c r="L65" s="22">
-        <v>191.60600829280901</v>
+        <v>191.60262307844954</v>
       </c>
       <c r="M65" s="21">
-        <v>498.005167388789</v>
+        <v>497.95800006871411</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="14.1" customHeight="1">
@@ -61739,16 +62176,16 @@
         <v>0.89446714184961917</v>
       </c>
       <c r="J66" s="22">
-        <v>307.50765051667753</v>
+        <v>307.46386841096211</v>
       </c>
       <c r="K66" s="22">
-        <v>499.19520733105378</v>
+        <v>499.14804001097889</v>
       </c>
       <c r="L66" s="22">
-        <v>191.68755681437625</v>
+        <v>191.68417160001678</v>
       </c>
       <c r="M66" s="21">
-        <v>498.30074018920413</v>
+        <v>498.25357286912924</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="14.1" customHeight="1">
@@ -61780,16 +62217,16 @@
         <v>0.85586449205052773</v>
       </c>
       <c r="J67" s="22">
-        <v>307.50765051667753</v>
+        <v>307.46386841096211</v>
       </c>
       <c r="K67" s="22">
-        <v>499.15743304036585</v>
+        <v>499.11026572029095</v>
       </c>
       <c r="L67" s="22">
-        <v>191.64978252368832</v>
+        <v>191.64639730932885</v>
       </c>
       <c r="M67" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="14.1" customHeight="1">
@@ -61821,16 +62258,16 @@
         <v>1.5788924406708102</v>
       </c>
       <c r="J68" s="22">
-        <v>308.28621714077974</v>
+        <v>308.24243503506432</v>
       </c>
       <c r="K68" s="22">
-        <v>499.88046098898616</v>
+        <v>499.83329366891127</v>
       </c>
       <c r="L68" s="22">
-        <v>191.59424384820642</v>
+        <v>191.59085863384695</v>
       </c>
       <c r="M68" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="14.1" customHeight="1">
@@ -61862,16 +62299,16 @@
         <v>6.7494303116673322</v>
       </c>
       <c r="J69" s="22">
-        <v>313.60003528991899</v>
+        <v>313.55625318420357</v>
       </c>
       <c r="K69" s="22">
-        <v>505.05099885998266</v>
+        <v>505.00383153990776</v>
       </c>
       <c r="L69" s="22">
-        <v>191.45096357006366</v>
+        <v>191.4475783557042</v>
       </c>
       <c r="M69" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="14.1" customHeight="1">
@@ -61903,16 +62340,16 @@
         <v>9.9133733862040057</v>
       </c>
       <c r="J70" s="22">
-        <v>316.4535834723722</v>
+        <v>316.40980136665678</v>
       </c>
       <c r="K70" s="22">
-        <v>508.21494193451935</v>
+        <v>508.16777461444445</v>
       </c>
       <c r="L70" s="22">
-        <v>191.76135846214714</v>
+        <v>191.75797324778767</v>
       </c>
       <c r="M70" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="14.1" customHeight="1">
@@ -61944,16 +62381,16 @@
         <v>10.495259866793916</v>
       </c>
       <c r="J71" s="22">
-        <v>316.71089770248</v>
+        <v>316.66711559676457</v>
       </c>
       <c r="K71" s="22">
-        <v>508.79682841510925</v>
+        <v>508.74966109503436</v>
       </c>
       <c r="L71" s="22">
-        <v>192.08593071262925</v>
+        <v>192.08254549826978</v>
       </c>
       <c r="M71" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="14.1" customHeight="1">
@@ -61985,16 +62422,16 @@
         <v>11.214216732390026</v>
       </c>
       <c r="J72" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K72" s="22">
-        <v>509.51578528070536</v>
+        <v>509.46861796063047</v>
       </c>
       <c r="L72" s="22">
-        <v>192.00037206169367</v>
+        <v>191.9969868473342</v>
       </c>
       <c r="M72" s="21">
-        <v>498.30156854831534</v>
+        <v>498.25440122824045</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="14.1" customHeight="1">
@@ -62026,16 +62463,16 @@
         <v>12.395947143481509</v>
       </c>
       <c r="J73" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K73" s="22">
-        <v>510.7754646513003</v>
+        <v>510.72829733122541</v>
       </c>
       <c r="L73" s="22">
-        <v>193.26005143228861</v>
+        <v>193.25666621792914</v>
       </c>
       <c r="M73" s="21">
-        <v>498.37951750781878</v>
+        <v>498.33235018774388</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="14.1" customHeight="1">
@@ -62067,16 +62504,16 @@
         <v>11.954148917418175</v>
       </c>
       <c r="J74" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K74" s="22">
-        <v>511.3962796036538</v>
+        <v>511.3491122835789</v>
       </c>
       <c r="L74" s="22">
-        <v>193.8808663846421</v>
+        <v>193.87748117028264</v>
       </c>
       <c r="M74" s="21">
-        <v>499.4421306862356</v>
+        <v>499.39496336616071</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="14.1" customHeight="1">
@@ -62108,16 +62545,16 @@
         <v>0</v>
       </c>
       <c r="J75" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K75" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L75" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M75" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="14.1" customHeight="1">
@@ -62149,16 +62586,16 @@
         <v>0</v>
       </c>
       <c r="J76" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K76" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L76" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M76" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="12.75">
@@ -62190,16 +62627,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K77" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L77" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M77" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="12.75">
@@ -62231,16 +62668,16 @@
         <v>0</v>
       </c>
       <c r="J78" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K78" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L78" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M78" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="12.75">
@@ -62272,16 +62709,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K79" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L79" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M79" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="12.75">
@@ -62313,16 +62750,16 @@
         <v>0</v>
       </c>
       <c r="J80" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K80" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L80" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M80" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="12.75">
@@ -62354,16 +62791,16 @@
         <v>0</v>
       </c>
       <c r="J81" s="22">
-        <v>317.51541321901169</v>
+        <v>317.47163111329627</v>
       </c>
       <c r="K81" s="22">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
       <c r="L81" s="22">
-        <v>195.67538981277875</v>
+        <v>195.67200459841928</v>
       </c>
       <c r="M81" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="12.75">
@@ -62395,16 +62832,16 @@
         <v>0.22000306970429231</v>
       </c>
       <c r="J82" s="22">
-        <v>317.73541628871601</v>
+        <v>317.69163418300059</v>
       </c>
       <c r="K82" s="22">
-        <v>513.4108061014947</v>
+        <v>513.36363878141981</v>
       </c>
       <c r="L82" s="22">
-        <v>195.67538981277869</v>
+        <v>195.67200459841922</v>
       </c>
       <c r="M82" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="12.75">
@@ -62436,16 +62873,16 @@
         <v>0.2309647808611083</v>
       </c>
       <c r="J83" s="22">
-        <v>317.74076568201389</v>
+        <v>317.69698357629846</v>
       </c>
       <c r="K83" s="22">
-        <v>513.42176781265152</v>
+        <v>513.37460049257663</v>
       </c>
       <c r="L83" s="22">
-        <v>195.68100213063764</v>
+        <v>195.67761691627817</v>
       </c>
       <c r="M83" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="12.75">
@@ -62477,16 +62914,16 @@
         <v>0.2476046408781975</v>
       </c>
       <c r="J84" s="22">
-        <v>317.75778856327963</v>
+        <v>317.71400645756421</v>
       </c>
       <c r="K84" s="22">
-        <v>513.43840767266863</v>
+        <v>513.39124035259374</v>
       </c>
       <c r="L84" s="22">
-        <v>195.680619109389</v>
+        <v>195.67723389502953</v>
       </c>
       <c r="M84" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="12.75">
@@ -62518,16 +62955,16 @@
         <v>28.570048006998732</v>
       </c>
       <c r="J85" s="22">
-        <v>346.12732616203544</v>
+        <v>346.08354405632002</v>
       </c>
       <c r="K85" s="22">
-        <v>541.76085103878916</v>
+        <v>541.71368371871426</v>
       </c>
       <c r="L85" s="22">
-        <v>195.63352487675371</v>
+        <v>195.63013966239424</v>
       </c>
       <c r="M85" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="12.75">
@@ -62559,16 +62996,16 @@
         <v>35.12375088595347</v>
       </c>
       <c r="J86" s="22">
-        <v>346.35166585996393</v>
+        <v>346.30788375424851</v>
       </c>
       <c r="K86" s="22">
-        <v>548.31455391774386</v>
+        <v>548.26738659766897</v>
       </c>
       <c r="L86" s="22">
-        <v>201.96288805777994</v>
+        <v>201.95950284342047</v>
       </c>
       <c r="M86" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="12.75">
@@ -62600,16 +63037,16 @@
         <v>35.2327855054628</v>
       </c>
       <c r="J87" s="22">
-        <v>346.43120812626563</v>
+        <v>346.38742602055021</v>
       </c>
       <c r="K87" s="22">
-        <v>548.42358853725318</v>
+        <v>548.3764212171784</v>
       </c>
       <c r="L87" s="22">
-        <v>201.99238041098755</v>
+        <v>201.9889951966282</v>
       </c>
       <c r="M87" s="21">
-        <v>513.19080303179044</v>
+        <v>513.14363571171555</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="12.75">
@@ -62641,16 +63078,16 @@
         <v>35.979887486370352</v>
       </c>
       <c r="J88" s="22">
-        <v>346.43120812626563</v>
+        <v>346.38742602055021</v>
       </c>
       <c r="K88" s="22">
-        <v>549.25120419774407</v>
+        <v>549.20403687766918</v>
       </c>
       <c r="L88" s="22">
-        <v>202.81999607147844</v>
+        <v>202.81661085711897</v>
       </c>
       <c r="M88" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="12.75">
@@ -62682,16 +63119,16 @@
         <v>34.671329374135034</v>
       </c>
       <c r="J89" s="22">
-        <v>347.15757819781584</v>
+        <v>347.11379609210042</v>
       </c>
       <c r="K89" s="22">
-        <v>547.94264608550873</v>
+        <v>547.89547876543384</v>
       </c>
       <c r="L89" s="22">
-        <v>200.78506788769289</v>
+        <v>200.78168267333342</v>
       </c>
       <c r="M89" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="12.75">
@@ -62723,16 +63160,16 @@
         <v>35.503258636049189</v>
       </c>
       <c r="J90" s="22">
-        <v>347.83889366468429</v>
+        <v>347.79511155896887</v>
       </c>
       <c r="K90" s="22">
-        <v>548.77457534742291</v>
+        <v>548.72740802734802</v>
       </c>
       <c r="L90" s="22">
-        <v>200.93568168273862</v>
+        <v>200.93229646837915</v>
       </c>
       <c r="M90" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="12.75">
@@ -62764,16 +63201,16 @@
         <v>36.308325460441139</v>
       </c>
       <c r="J91" s="22">
-        <v>348.92037187089284</v>
+        <v>348.87658976517741</v>
       </c>
       <c r="K91" s="22">
-        <v>549.57964217181484</v>
+        <v>549.53247485173995</v>
       </c>
       <c r="L91" s="22">
-        <v>200.659270300922</v>
+        <v>200.65588508656253</v>
       </c>
       <c r="M91" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="12.75">
@@ -62805,16 +63242,16 @@
         <v>50.522807320120393</v>
       </c>
       <c r="J92" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K92" s="22">
-        <v>563.79412403149411</v>
+        <v>563.74695671141922</v>
       </c>
       <c r="L92" s="22">
-        <v>197.36714737913957</v>
+        <v>197.3637621647801</v>
       </c>
       <c r="M92" s="21">
-        <v>513.27131671137374</v>
+        <v>513.22414939129885</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="12.75">
@@ -62846,16 +63283,16 @@
         <v>37.983849564585157</v>
       </c>
       <c r="J93" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K93" s="22">
-        <v>576.14629645503999</v>
+        <v>576.0991291349651</v>
       </c>
       <c r="L93" s="22">
-        <v>209.71931980268545</v>
+        <v>209.71593458832598</v>
       </c>
       <c r="M93" s="21">
-        <v>538.16244689045482</v>
+        <v>538.11527957037993</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="12.75">
@@ -62887,16 +63324,16 @@
         <v>0</v>
       </c>
       <c r="J94" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K94" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L94" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M94" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="12.75">
@@ -62928,16 +63365,16 @@
         <v>0</v>
       </c>
       <c r="J95" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K95" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L95" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M95" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="12.75">
@@ -62969,16 +63406,16 @@
         <v>0</v>
       </c>
       <c r="J96" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K96" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L96" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M96" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="12.75">
@@ -63010,16 +63447,16 @@
         <v>0</v>
       </c>
       <c r="J97" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K97" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L97" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M97" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="12.75">
@@ -63051,16 +63488,16 @@
         <v>0</v>
       </c>
       <c r="J98" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K98" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L98" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M98" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="12.75">
@@ -63092,16 +63529,16 @@
         <v>0</v>
       </c>
       <c r="J99" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K99" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L99" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M99" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="12.75">
@@ -63133,16 +63570,16 @@
         <v>0</v>
       </c>
       <c r="J100" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K100" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L100" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M100" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="12.75">
@@ -63174,16 +63611,16 @@
         <v>0</v>
       </c>
       <c r="J101" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K101" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L101" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M101" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="12.75">
@@ -63215,16 +63652,16 @@
         <v>0</v>
       </c>
       <c r="J102" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K102" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L102" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M102" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="12.75">
@@ -63256,16 +63693,16 @@
         <v>0</v>
       </c>
       <c r="J103" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K103" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L103" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M103" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="12.75">
@@ -63297,16 +63734,16 @@
         <v>0</v>
       </c>
       <c r="J104" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K104" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L104" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M104" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="12.75">
@@ -63338,16 +63775,16 @@
         <v>0</v>
       </c>
       <c r="J105" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K105" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L105" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M105" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="12.75">
@@ -63379,16 +63816,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K106" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L106" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M106" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="12.75">
@@ -63420,16 +63857,16 @@
         <v>0</v>
       </c>
       <c r="J107" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K107" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L107" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M107" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="12.75">
@@ -63461,16 +63898,16 @@
         <v>0</v>
       </c>
       <c r="J108" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K108" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L108" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M108" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="12.75">
@@ -63502,16 +63939,16 @@
         <v>0</v>
       </c>
       <c r="J109" s="22">
-        <v>366.42697665235454</v>
+        <v>366.38319454663912</v>
       </c>
       <c r="K109" s="22">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
       <c r="L109" s="22">
-        <v>212.99681655802686</v>
+        <v>212.9934313436674</v>
       </c>
       <c r="M109" s="21">
-        <v>579.4237932103814</v>
+        <v>579.37662589030651</v>
       </c>
     </row>
   </sheetData>
